--- a/client/public/student-template.xlsx
+++ b/client/public/student-template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20400" windowHeight="7770"/>
+    <workbookView windowWidth="20490" windowHeight="7770"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Full Name</t>
   </si>
@@ -35,6 +35,9 @@
     <t>Gender</t>
   </si>
   <si>
+    <t>year</t>
+  </si>
+  <si>
     <t>Date of Birth</t>
   </si>
   <si>
@@ -51,6 +54,9 @@
   </si>
   <si>
     <t>Father Contact</t>
+  </si>
+  <si>
+    <t>National Id</t>
   </si>
   <si>
     <t xml:space="preserve">Tomas Medihne </t>
@@ -755,7 +761,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1275,19 +1281,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="30.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="14.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="13.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="18.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="18.2857142857143" customWidth="1"/>
-    <col min="7" max="7" width="15.7142857142857" customWidth="1"/>
-    <col min="8" max="8" width="17.7142857142857" customWidth="1"/>
+    <col min="3" max="4" width="14.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="13.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="18.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="18.2857142857143" customWidth="1"/>
+    <col min="8" max="8" width="15.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="17.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1306,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1312,67 +1318,79 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4">
         <v>42085</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
         <v>42086</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="4" spans="3:3">
+    <row r="4" spans="1:10">
       <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="3:3">
+    <row r="5" spans="1:10">
       <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="3:3">
+    <row r="6" spans="1:10">
       <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="3:3">
+    <row r="7" spans="1:10">
       <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
